--- a/SURFv6revC/surfv6c_design_bom.xlsx
+++ b/SURFv6revC/surfv6c_design_bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\pueo-daq-design\SURFv6revC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13841DD-0D57-43DC-AF31-95BAE460D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D822D646-9072-4743-A68C-CB291B69D924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2593546-CCEE-4E66-8A39-06F8C8F9796E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2593546-CCEE-4E66-8A39-06F8C8F9796E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="361">
   <si>
     <t>J12</t>
   </si>
@@ -1110,9 +1110,6 @@
   </si>
   <si>
     <t>4-bit dual-supply bus transceiver with 3-state outputs and independent direction control inputs</t>
-  </si>
-  <si>
-    <t>TCM2-33WX+</t>
   </si>
   <si>
     <t>DT1446-04S-7</t>
@@ -2383,7 +2380,7 @@
         <v>347</v>
       </c>
       <c r="E42" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F42" t="s">
         <v>187</v>
@@ -2974,10 +2971,10 @@
         <v>202</v>
       </c>
       <c r="E69" t="s">
+        <v>359</v>
+      </c>
+      <c r="F69" t="s">
         <v>360</v>
-      </c>
-      <c r="F69" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -3613,7 +3610,7 @@
         <v>289</v>
       </c>
       <c r="E99" t="s">
-        <v>358</v>
+        <v>289</v>
       </c>
       <c r="F99" t="s">
         <v>114</v>
